--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE86B713-DE59-4B64-8797-3DD912D51B95}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8E5B40-F9C6-4C9F-886F-2A1BAE947FD3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
   <sheets>
     <sheet name="data_mat_proj" sheetId="1" r:id="rId1"/>
     <sheet name="data_proj" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_mat_proj!$A$1:$C$36</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -167,10 +170,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,7 +583,7 @@
         <v>2026</v>
       </c>
       <c r="C8">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,7 +660,7 @@
         <v>2026</v>
       </c>
       <c r="C15">
-        <v>667</v>
+        <v>674</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="C22">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,7 +891,7 @@
         <v>2026</v>
       </c>
       <c r="C36">
-        <v>914</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -927,7 +926,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -938,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -949,7 +948,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,7 +992,7 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1004,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,7 +1025,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1048,7 +1047,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1059,7 +1058,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1081,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1092,7 +1091,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1103,7 +1102,7 @@
         <v>11</v>
       </c>
       <c r="C18">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1147,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1169,7 +1168,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1180,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1191,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1202,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1235,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="C30">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1246,7 +1245,7 @@
         <v>14</v>
       </c>
       <c r="C31">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1257,7 +1256,7 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1268,7 +1267,7 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1279,7 +1278,7 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1301,7 +1300,7 @@
         <v>18</v>
       </c>
       <c r="C36">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,7 +1311,7 @@
         <v>19</v>
       </c>
       <c r="C37">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1323,7 +1322,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8E5B40-F9C6-4C9F-886F-2A1BAE947FD3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
   <sheets>
     <sheet name="data_mat_proj" sheetId="1" r:id="rId1"/>
@@ -170,6 +170,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
